--- a/lessons/sorting/excels/remarks_leo.xlsx
+++ b/lessons/sorting/excels/remarks_leo.xlsx
@@ -162,12 +162,12 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -- (10:57:30.402), -end (10:57:30.432), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~0.00, -align (10:57:30.272) ~0.30, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~0.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.33, +justify (00:00:00), +content (00:00:00), +center (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
+        <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -187,7 +187,7 @@
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>-var (10:59:12.196), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
+        <t>-var (10:59:12.196) ~0.00, -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -207,7 +207,7 @@
     </comment>
     <comment ref="M9" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), -Visualizer (10:13:16.993), +visualizer (00:00:00), +visualizer (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, -Visualizer (10:13:16.993) ~0.90, +visualizer (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O9" authorId="0" shapeId="0">
@@ -217,7 +217,7 @@
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>-; (11:08:34.198), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+        <t>-; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
@@ -267,17 +267,17 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-0px (10:48:03.827), +0 (00:00:00)</t>
+        <t>-0px (10:48:03.827) ~0.33, +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+        <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H24" authorId="0" shapeId="0">
@@ -317,7 +317,7 @@
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H30" authorId="0" shapeId="0">
@@ -342,12 +342,12 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+        <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q31" authorId="0" shapeId="0">
       <text>
-        <t>-1 (10:59:28.458), +0 (00:00:00)</t>
+        <t>-1 (10:59:28.458) ~0.00, +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -367,7 +367,7 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+        <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
@@ -377,7 +377,7 @@
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+        <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -397,7 +397,7 @@
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-column (10:22:03.223), +coloumn (00:00:00)</t>
+        <t>-column (10:22:03.223) ~0.86, +coloumn (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q42" authorId="0" shapeId="0">
@@ -442,7 +442,7 @@
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -display (10:47:38.305), -: (10:47:38.437), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
+        <t>-flex (10:21:58.800), -display (10:47:38.305) ~0.14, -: (10:47:38.437) ~1.00, +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
@@ -457,17 +457,17 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
+        <t>-flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437) ~1.00, -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -- (10:57:30.282) ~1.00, -: (10:57:30.342) ~1.00, -- (10:57:30.402), -end (10:57:30.432) ~0.33, -; (10:57:30.442), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -document (10:37:47.323), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arry (00:00:00), +) (00:00:00), +; (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arry (00:00:00), +) (00:00:00), +; (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -487,7 +487,7 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-html (10:12:23.484), +htm (00:00:00)</t>
+        <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
@@ -497,7 +497,7 @@
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924), +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
+        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H51" authorId="0" shapeId="0">
@@ -527,7 +527,7 @@
     </comment>
     <comment ref="Q56" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
@@ -547,17 +547,17 @@
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:20:09.451), -: (10:47:38.437), -- (10:57:30.402), +- (00:00:00), +: (00:00:00), +; (00:00:00)</t>
+        <t>-; (10:20:09.451), -: (10:47:38.437) ~1.00, -- (10:57:30.402), +- (00:00:00), +: (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="H62" authorId="0" shapeId="0">
@@ -582,7 +582,7 @@
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
       <text>
-        <t>-7px (10:43:39.527), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
+        <t>-7px (10:43:39.527) ~0.60, +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q66" authorId="0" shapeId="0">
@@ -607,12 +607,12 @@
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-0px (10:48:03.827), +: (00:00:00), +; (00:00:00), +background (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
+        <t>-0px (10:48:03.827) ~0.33, +: (00:00:00), +; (00:00:00), +background (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920), -getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -updateBars (11:12:30.664), -100 (11:14:24.924), +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993), -updateBars (11:12:30.664) ~0.90, -100 (11:14:24.924) ~0.67, +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -632,17 +632,17 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+        <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-200px (10:20:09.051), -background (10:44:24.231), +500px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +Background (00:00:00)</t>
+        <t>-200px (10:20:09.051) ~0.80, -background (10:44:24.231) ~0.90, +500px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +Background (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="J71" authorId="0" shapeId="0">
@@ -672,17 +672,17 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-123456 (10:19:55.544), -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +654321 (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
+        <t>-123456 (10:19:55.544) ~0.00, -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -- (10:57:30.282) ~1.00, -: (10:57:30.342) ~1.00, -- (10:57:30.402), -end (10:57:30.432) ~0.33, -; (10:57:30.442), +654321 (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -document (10:37:47.323), -123456 (10:38:22.251), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arry (00:00:00), +) (00:00:00), +; (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -123456 (10:38:22.251) ~0.00, -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arry (00:00:00), +) (00:00:00), +; (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="J73" authorId="0" shapeId="0">
@@ -707,12 +707,12 @@
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:47:39.811), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:47:39.811) ~1.00, -- (10:57:30.282) ~1.00, -: (10:57:30.342) ~1.00, -- (10:57:30.402), -end (10:57:30.432) ~0.33, +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q75" authorId="0" shapeId="0">
       <text>
-        <t>-createElement (10:39:45.021), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857), +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+        <t>-createElement (10:39:45.021) ~0.93, -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -752,7 +752,7 @@
     </comment>
     <comment ref="Q79" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H81" authorId="0" shapeId="0">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -- (10:57:30.402), -end (10:57:30.432), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~0.00, -align (10:57:30.272) ~0.30, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~0.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.33, +justify (00:00:00), +content (00:00:00), +center (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
+          <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-var (10:59:12.196), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
+          <t>-var (10:59:12.196) ~0.00, -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), -Visualizer (10:13:16.993), +visualizer (00:00:00), +visualizer (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, -Visualizer (10:13:16.993) ~0.90, +visualizer (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-; (11:08:34.198), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+          <t>-; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-0px (10:48:03.827), +0 (00:00:00)</t>
+          <t>-0px (10:48:03.827) ~0.33, +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+          <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+          <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>-1 (10:59:28.458), +0 (00:00:00)</t>
+          <t>-1 (10:59:28.458) ~0.00, +0 (00:00:00)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+          <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+          <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-column (10:22:03.223), +coloumn (00:00:00)</t>
+          <t>-column (10:22:03.223) ~0.86, +coloumn (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -display (10:47:38.305), -: (10:47:38.437), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
+          <t>-flex (10:21:58.800), -display (10:47:38.305) ~0.14, -: (10:47:38.437) ~1.00, +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
+          <t>-flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437) ~1.00, -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -- (10:57:30.282) ~1.00, -: (10:57:30.342) ~1.00, -- (10:57:30.402), -end (10:57:30.432) ~0.33, -; (10:57:30.442), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -document (10:37:47.323), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arry (00:00:00), +) (00:00:00), +; (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arry (00:00:00), +) (00:00:00), +; (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-html (10:12:23.484), +htm (00:00:00)</t>
+          <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924), +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
+          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-; (10:20:09.451), -: (10:47:38.437), -- (10:57:30.402), +- (00:00:00), +: (00:00:00), +; (00:00:00)</t>
+          <t>-; (10:20:09.451), -: (10:47:38.437) ~1.00, -- (10:57:30.402), +- (00:00:00), +: (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>-7px (10:43:39.527), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
+          <t>-7px (10:43:39.527) ~0.60, +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-0px (10:48:03.827), +: (00:00:00), +; (00:00:00), +background (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
+          <t>-0px (10:48:03.827) ~0.33, +: (00:00:00), +; (00:00:00), +background (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920), -getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -updateBars (11:12:30.664), -100 (11:14:24.924), +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993), -updateBars (11:12:30.664) ~0.90, -100 (11:14:24.924) ~0.67, +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+          <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-200px (10:20:09.051), -background (10:44:24.231), +500px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +Background (00:00:00)</t>
+          <t>-200px (10:20:09.051) ~0.80, -background (10:44:24.231) ~0.90, +500px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +Background (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-123456 (10:19:55.544), -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +654321 (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
+          <t>-123456 (10:19:55.544) ~0.00, -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -- (10:57:30.282) ~1.00, -: (10:57:30.342) ~1.00, -- (10:57:30.402), -end (10:57:30.432) ~0.33, -; (10:57:30.442), +654321 (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -document (10:37:47.323), -123456 (10:38:22.251), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arry (00:00:00), +) (00:00:00), +; (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -123456 (10:38:22.251) ~0.00, -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arry (00:00:00), +) (00:00:00), +; (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:47:39.811), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:47:39.811) ~1.00, -- (10:57:30.282) ~1.00, -: (10:57:30.342) ~1.00, -- (10:57:30.402), -end (10:57:30.432) ~0.33, +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>-createElement (10:39:45.021), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857), +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+          <t>-createElement (10:39:45.021) ~0.93, -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
